--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T17:12:42+00:00</t>
+    <t>2025-11-10T13:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-10T13:55:53+00:00</t>
+    <t>2025-11-18T09:59:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T09:59:03+00:00</t>
+    <t>2025-11-18T10:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:10:09+00:00</t>
+    <t>2025-11-18T10:37:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:37:29+00:00</t>
+    <t>2025-11-18T10:47:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T10:47:05+00:00</t>
+    <t>2025-11-18T14:02:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T14:02:28+00:00</t>
+    <t>2025-11-18T15:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T15:51:09+00:00</t>
+    <t>2025-11-18T15:52:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T15:52:49+00:00</t>
+    <t>2025-11-18T16:02:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
+++ b/DescriptionMetier/ig/CodeSystem-fr-note-scope-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-18T16:02:22+00:00</t>
+    <t>2025-11-25T08:13:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
